--- a/data/trans_orig/IP22D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Edad-trans_orig.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18303</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96452</t>
+          <t>96686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6261</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8334</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7028</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12014</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10221</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12537</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14175</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10080</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15794</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12662</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16719</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5495</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,64 +1749,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19721</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17756</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17541</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47147</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43052</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51824</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48424</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53272</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>90178</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96686</t>
+          <t>86312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4848</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
